--- a/artfynd/A 13244-2026 artfynd.xlsx
+++ b/artfynd/A 13244-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118793372</v>
+        <v>118793575</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879147</v>
+        <v>878997</v>
       </c>
       <c r="R2" t="n">
-        <v>7410683</v>
+        <v>7410593</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,12 +751,18 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118793584</v>
+        <v>118793359</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3277</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879242</v>
+        <v>879308</v>
       </c>
       <c r="R3" t="n">
-        <v>7410814</v>
+        <v>7410737</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118793359</v>
+        <v>118793362</v>
       </c>
       <c r="B4" t="n">
-        <v>90567</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3277</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879308</v>
+        <v>879153</v>
       </c>
       <c r="R4" t="n">
-        <v>7410737</v>
+        <v>7410579</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,37 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118793580</v>
+        <v>118793363</v>
       </c>
       <c r="B5" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879242</v>
+        <v>879291</v>
       </c>
       <c r="R5" t="n">
-        <v>7410815</v>
+        <v>7410669</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1057,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118793585</v>
+        <v>118793364</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879078</v>
+        <v>879242</v>
       </c>
       <c r="R6" t="n">
-        <v>7410852</v>
+        <v>7410815</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,37 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118793578</v>
+        <v>118793365</v>
       </c>
       <c r="B7" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879261</v>
+        <v>879126</v>
       </c>
       <c r="R7" t="n">
-        <v>7410686</v>
+        <v>7410862</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1240,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,19 +1266,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793373</v>
+        <v>118793366</v>
       </c>
       <c r="B8" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1337,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879116</v>
+        <v>879121</v>
       </c>
       <c r="R8" t="n">
-        <v>7410673</v>
+        <v>7410856</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,37 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793589</v>
+        <v>118793367</v>
       </c>
       <c r="B9" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879066</v>
+        <v>879104</v>
       </c>
       <c r="R9" t="n">
-        <v>7410571</v>
+        <v>7410851</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,19 +1460,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793364</v>
+        <v>118793368</v>
       </c>
       <c r="B10" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1541,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879242</v>
+        <v>879068</v>
       </c>
       <c r="R10" t="n">
-        <v>7410815</v>
+        <v>7410854</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,19 +1557,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793366</v>
+        <v>118793370</v>
       </c>
       <c r="B11" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1643,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879121</v>
+        <v>879185</v>
       </c>
       <c r="R11" t="n">
-        <v>7410856</v>
+        <v>7410814</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,37 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793586</v>
+        <v>118793371</v>
       </c>
       <c r="B12" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879119</v>
+        <v>879153</v>
       </c>
       <c r="R12" t="n">
-        <v>7410609</v>
+        <v>7410722</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1807,37 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118793588</v>
+        <v>118793372</v>
       </c>
       <c r="B13" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879064</v>
+        <v>879147</v>
       </c>
       <c r="R13" t="n">
-        <v>7410567</v>
+        <v>7410683</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1909,37 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118793577</v>
+        <v>118793373</v>
       </c>
       <c r="B14" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879114</v>
+        <v>879116</v>
       </c>
       <c r="R14" t="n">
-        <v>7410564</v>
+        <v>7410673</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1985,11 +1919,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,54 +1945,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118794496</v>
+        <v>118793374</v>
       </c>
       <c r="B15" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879055</v>
+        <v>879113</v>
       </c>
       <c r="R15" t="n">
-        <v>7410850</v>
+        <v>7410609</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2096,11 +2016,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,19 +2042,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118793374</v>
+        <v>118793377</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2167,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879113</v>
+        <v>879103</v>
       </c>
       <c r="R16" t="n">
-        <v>7410609</v>
+        <v>7410568</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2229,37 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118793367</v>
+        <v>118793587</v>
       </c>
       <c r="B17" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879104</v>
+        <v>879116</v>
       </c>
       <c r="R17" t="n">
-        <v>7410851</v>
+        <v>7410673</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2331,37 +2236,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118793363</v>
+        <v>118793588</v>
       </c>
       <c r="B18" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879291</v>
+        <v>879064</v>
       </c>
       <c r="R18" t="n">
-        <v>7410669</v>
+        <v>7410567</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2433,37 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118793362</v>
+        <v>118793589</v>
       </c>
       <c r="B19" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879153</v>
+        <v>879066</v>
       </c>
       <c r="R19" t="n">
-        <v>7410579</v>
+        <v>7410571</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2535,37 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118793368</v>
+        <v>118793584</v>
       </c>
       <c r="B20" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879068</v>
+        <v>879242</v>
       </c>
       <c r="R20" t="n">
-        <v>7410854</v>
+        <v>7410814</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2637,37 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118793370</v>
+        <v>118793585</v>
       </c>
       <c r="B21" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879185</v>
+        <v>879078</v>
       </c>
       <c r="R21" t="n">
-        <v>7410814</v>
+        <v>7410852</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2739,37 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118793360</v>
+        <v>118793586</v>
       </c>
       <c r="B22" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>879042</v>
+        <v>879119</v>
       </c>
       <c r="R22" t="n">
-        <v>7410510</v>
+        <v>7410609</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2815,11 +2695,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2846,15 +2721,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118793377</v>
+        <v>118793577</v>
       </c>
       <c r="B23" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,21 +2732,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>879103</v>
+        <v>879114</v>
       </c>
       <c r="R23" t="n">
-        <v>7410568</v>
+        <v>7410564</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2922,6 +2792,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,15 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118793371</v>
+        <v>118793578</v>
       </c>
       <c r="B24" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>879153</v>
+        <v>879261</v>
       </c>
       <c r="R24" t="n">
-        <v>7410722</v>
+        <v>7410686</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3024,6 +2894,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3053,12 +2928,7 @@
         <v>118793579</v>
       </c>
       <c r="B25" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,15 +3027,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118793365</v>
+        <v>118793580</v>
       </c>
       <c r="B26" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3173,21 +3038,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3197,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>879126</v>
+        <v>879242</v>
       </c>
       <c r="R26" t="n">
-        <v>7410862</v>
+        <v>7410815</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3233,6 +3098,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3259,50 +3129,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118793587</v>
+        <v>118794496</v>
       </c>
       <c r="B27" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>879116</v>
+        <v>879055</v>
       </c>
       <c r="R27" t="n">
-        <v>7410673</v>
+        <v>7410850</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3335,6 +3204,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 13244-2026 artfynd.xlsx
+++ b/artfynd/A 13244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793363</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793364</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793365</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793366</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793368</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793370</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793371</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793372</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793374</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793377</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793587</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793588</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793589</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793584</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793585</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793586</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793577</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793578</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793579</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3126,6 +3251,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118793580</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3232,8 +3362,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118794496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>